--- a/research/traditional_assets/database/data/colombia/colombia_apparel.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_apparel.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.04269999999999999</v>
+        <v>-0.476</v>
       </c>
       <c r="G2">
-        <v>-0.1875792141951838</v>
+        <v>-4.193370165745856</v>
       </c>
       <c r="H2">
-        <v>-0.1875792141951838</v>
+        <v>-4.193370165745856</v>
       </c>
       <c r="I2">
-        <v>-0.191381495564005</v>
+        <v>-4.359116022099447</v>
       </c>
       <c r="J2">
-        <v>-0.191381495564005</v>
+        <v>-4.359116022099447</v>
       </c>
       <c r="K2">
-        <v>-20.6</v>
+        <v>-28.4</v>
       </c>
       <c r="L2">
-        <v>-0.2610899873257287</v>
+        <v>-15.69060773480663</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.454</v>
+        <v>0.063</v>
       </c>
       <c r="V2">
-        <v>0.02467391304347826</v>
+        <v>0.003888888888888889</v>
       </c>
       <c r="W2">
-        <v>-0.1640127388535032</v>
+        <v>-0.1858638743455497</v>
       </c>
       <c r="X2">
-        <v>0.1334223087655812</v>
+        <v>0.1164361469842141</v>
       </c>
       <c r="Y2">
-        <v>-0.2974350476190843</v>
+        <v>-0.3023000213297637</v>
       </c>
       <c r="Z2">
-        <v>0.5107854053914079</v>
+        <v>0.01191636162536539</v>
       </c>
       <c r="AA2">
-        <v>-0.09775487479607425</v>
+        <v>-0.05194480288626128</v>
       </c>
       <c r="AB2">
-        <v>0.06754140324751805</v>
+        <v>0.1164361469842141</v>
       </c>
       <c r="AC2">
-        <v>-0.1652962780435923</v>
+        <v>-0.1683809498704753</v>
       </c>
       <c r="AD2">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>32.246</v>
+        <v>-0.063</v>
       </c>
       <c r="AH2">
-        <v>0.639921722113503</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.2174202127659575</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.63669391462307</v>
+        <v>-0.003904071388733965</v>
       </c>
       <c r="AK2">
-        <v>0.2150507516039108</v>
+        <v>-0.000579379603998639</v>
       </c>
       <c r="AL2">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
       <c r="AM2">
-        <v>4.175</v>
+        <v>4.13</v>
       </c>
       <c r="AN2">
-        <v>-2.747899159663866</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-3.511627906976744</v>
+        <v>-1.910411622276029</v>
       </c>
       <c r="AP2">
-        <v>-2.709747899159664</v>
+        <v>0.008961593172119487</v>
       </c>
       <c r="AQ2">
-        <v>-3.616766467065868</v>
+        <v>-1.910411622276029</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fabricato S.A. (BVC:FABRICATO)</t>
+          <t>Coltejer S.A. (BVC:COLTEJER)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.04269999999999999</v>
+        <v>-0.476</v>
       </c>
       <c r="G3">
-        <v>-0.1875792141951838</v>
+        <v>-4.193370165745856</v>
       </c>
       <c r="H3">
-        <v>-0.1875792141951838</v>
+        <v>-4.193370165745856</v>
       </c>
       <c r="I3">
-        <v>-0.191381495564005</v>
+        <v>-4.359116022099447</v>
       </c>
       <c r="J3">
-        <v>-0.191381495564005</v>
+        <v>-4.359116022099447</v>
       </c>
       <c r="K3">
-        <v>-20.6</v>
+        <v>-28.4</v>
       </c>
       <c r="L3">
-        <v>-0.2610899873257287</v>
+        <v>-15.69060773480663</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.454</v>
+        <v>0.063</v>
       </c>
       <c r="V3">
-        <v>0.02467391304347826</v>
+        <v>0.003888888888888889</v>
       </c>
       <c r="W3">
-        <v>-0.1640127388535032</v>
+        <v>-0.1858638743455497</v>
       </c>
       <c r="X3">
-        <v>0.1334223087655812</v>
+        <v>0.1164361469842141</v>
       </c>
       <c r="Y3">
-        <v>-0.2974350476190843</v>
+        <v>-0.3023000213297637</v>
       </c>
       <c r="Z3">
-        <v>0.5107854053914079</v>
+        <v>0.01191636162536539</v>
       </c>
       <c r="AA3">
-        <v>-0.09775487479607425</v>
+        <v>-0.05194480288626128</v>
       </c>
       <c r="AB3">
-        <v>0.06754140324751805</v>
+        <v>0.1164361469842141</v>
       </c>
       <c r="AC3">
-        <v>-0.1652962780435923</v>
+        <v>-0.1683809498704753</v>
       </c>
       <c r="AD3">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>32.246</v>
+        <v>-0.063</v>
       </c>
       <c r="AH3">
-        <v>0.639921722113503</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.2174202127659575</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.63669391462307</v>
+        <v>-0.003904071388733965</v>
       </c>
       <c r="AK3">
-        <v>0.2150507516039108</v>
+        <v>-0.000579379603998639</v>
       </c>
       <c r="AL3">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
       <c r="AM3">
-        <v>4.175</v>
+        <v>4.13</v>
       </c>
       <c r="AN3">
-        <v>-2.747899159663866</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-3.511627906976744</v>
+        <v>-1.910411622276029</v>
       </c>
       <c r="AP3">
-        <v>-2.709747899159664</v>
+        <v>0.008961593172119487</v>
       </c>
       <c r="AQ3">
-        <v>-3.616766467065868</v>
+        <v>-1.910411622276029</v>
       </c>
     </row>
   </sheetData>
